--- a/resources/tool_kii_community_iphra_v2.xlsx
+++ b/resources/tool_kii_community_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A84014E-BFEE-44FD-BA02-CDE24A25E140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8DFBE0-F5CC-498B-9BD8-491F34B8C948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$B$1:$J$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$B$1:$J$99</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="299">
   <si>
     <t>type</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>Please specify enumerator ID</t>
-  </si>
-  <si>
-    <t>end_group</t>
   </si>
   <si>
     <t>select_one yes_no</t>
@@ -136,12 +133,6 @@
   </si>
   <si>
     <t>What is the respondent's contact information? (optional)</t>
-  </si>
-  <si>
-    <t>core_questions</t>
-  </si>
-  <si>
-    <t>Section 2: Core Questions</t>
   </si>
   <si>
     <t>select_one problem</t>
@@ -400,12 +391,6 @@
     <t>Write down the person’s answer</t>
   </si>
   <si>
-    <t>Priority_Problems</t>
-  </si>
-  <si>
-    <t>Priority Problems</t>
-  </si>
-  <si>
     <t>select_one top_priority_problem</t>
   </si>
   <si>
@@ -457,12 +442,6 @@
     <t>selected(${third_serious_problem},'other')</t>
   </si>
   <si>
-    <t>Supplemental_Questions</t>
-  </si>
-  <si>
-    <t>Section 3: Supplemental Questions</t>
-  </si>
-  <si>
     <t>distress_problem</t>
   </si>
   <si>
@@ -992,6 +971,12 @@
   </si>
   <si>
     <t>admin4c</t>
+  </si>
+  <si>
+    <t>comments_enum</t>
+  </si>
+  <si>
+    <t>Do you as the interviewer have any further comments or observations?</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1019,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1059,6 +1044,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1072,7 +1063,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1083,6 +1074,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1458,13 +1450,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="72.85546875" customWidth="1"/>
+    <col min="4" max="4" width="89" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" customWidth="1"/>
     <col min="8" max="8" width="24.7109375" customWidth="1"/>
@@ -1472,7 +1464,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1603,16 +1595,16 @@
         <v>10000</v>
       </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -1626,7 +1618,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1634,13 +1626,13 @@
         <v>10000</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1648,16 +1640,16 @@
         <v>10000</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1671,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1679,16 +1671,16 @@
         <v>10000</v>
       </c>
       <c r="B13" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C13" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -1702,10 +1694,10 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
         <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -1719,52 +1711,58 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
         <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>10000</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="3" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>13301</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s">
         <v>32</v>
       </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>42001</v>
+      <c r="A17" s="8">
+        <v>13301</v>
       </c>
       <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>34</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
         <v>35</v>
       </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>42001</v>
+      <c r="A18" s="8">
+        <v>13301</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
@@ -1779,15 +1777,18 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>42001</v>
+      <c r="A19" s="8">
+        <v>11301</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>39</v>
@@ -1795,39 +1796,36 @@
       <c r="D19" t="s">
         <v>40</v>
       </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>11301</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>22002</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>42</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
         <v>43</v>
       </c>
-      <c r="E20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>22002</v>
+      <c r="A21" s="8">
+        <v>11301</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
@@ -1842,121 +1840,121 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>12504</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>22002</v>
-      </c>
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>47</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>12504</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
         <v>48</v>
       </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>34001</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
         <v>49</v>
       </c>
-      <c r="D23" t="s">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>12504</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
         <v>50</v>
       </c>
-      <c r="E23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>34001</v>
-      </c>
-      <c r="B24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>51</v>
       </c>
-      <c r="D24" t="s">
-        <v>37</v>
-      </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>14803</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>34001</v>
-      </c>
-      <c r="B25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>53</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>14803</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
         <v>54</v>
       </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>57003</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
         <v>55</v>
       </c>
-      <c r="D26" t="s">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>14803</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
         <v>56</v>
       </c>
-      <c r="E26" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>57003</v>
-      </c>
-      <c r="B27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>57</v>
-      </c>
-      <c r="D27" t="s">
-        <v>37</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1966,11 +1964,11 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>57003</v>
+      <c r="A28" s="8">
+        <v>11103</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>59</v>
@@ -1978,1277 +1976,1289 @@
       <c r="D28" t="s">
         <v>60</v>
       </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
       <c r="F28" t="b">
         <v>1</v>
       </c>
-      <c r="G28" t="s">
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>11103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>20003</v>
-      </c>
-      <c r="B29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
         <v>62</v>
       </c>
-      <c r="D29" t="s">
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>11103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
         <v>63</v>
       </c>
-      <c r="E29" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>20003</v>
-      </c>
-      <c r="B30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>64</v>
       </c>
-      <c r="D30" t="s">
-        <v>37</v>
-      </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
       <c r="G30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>12505</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>20003</v>
-      </c>
-      <c r="B31" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>66</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>12505</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
         <v>67</v>
       </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>34101</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
         <v>68</v>
       </c>
-      <c r="D32" t="s">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>12505</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
         <v>69</v>
       </c>
-      <c r="E32" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>34101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>70</v>
       </c>
-      <c r="D33" t="s">
-        <v>37</v>
-      </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>12202</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>34101</v>
-      </c>
-      <c r="B34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>72</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>12202</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
         <v>73</v>
       </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>31002</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
         <v>74</v>
       </c>
-      <c r="D35" t="s">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>12202</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
         <v>75</v>
       </c>
-      <c r="E35" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>31002</v>
-      </c>
-      <c r="B36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>76</v>
       </c>
-      <c r="D36" t="s">
-        <v>37</v>
-      </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>10602</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>31002</v>
-      </c>
-      <c r="B37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>78</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>10602</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
         <v>79</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>15002</v>
-      </c>
-      <c r="B38" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
         <v>80</v>
       </c>
-      <c r="D38" t="s">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>10602</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
         <v>81</v>
       </c>
-      <c r="E38" t="s">
-        <v>26</v>
-      </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>15002</v>
-      </c>
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>82</v>
       </c>
-      <c r="D39" t="s">
-        <v>37</v>
-      </c>
       <c r="F39" t="b">
         <v>1</v>
       </c>
       <c r="G39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>14402</v>
+      </c>
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>15002</v>
-      </c>
-      <c r="B40" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>84</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>14402</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
         <v>85</v>
       </c>
-      <c r="F40" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>52102</v>
-      </c>
-      <c r="B41" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
         <v>86</v>
       </c>
-      <c r="D41" t="s">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>14402</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
         <v>87</v>
       </c>
-      <c r="E41" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>52102</v>
-      </c>
-      <c r="B42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>88</v>
       </c>
-      <c r="D42" t="s">
-        <v>37</v>
-      </c>
       <c r="F42" t="b">
         <v>1</v>
       </c>
       <c r="G42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>15101</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>52102</v>
-      </c>
-      <c r="B43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>15101</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
         <v>91</v>
       </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>58001</v>
-      </c>
-      <c r="B44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
         <v>92</v>
       </c>
-      <c r="D44" t="s">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>15101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
         <v>93</v>
       </c>
-      <c r="E44" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>58001</v>
-      </c>
-      <c r="B45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>94</v>
       </c>
-      <c r="D45" t="s">
-        <v>37</v>
-      </c>
       <c r="F45" t="b">
         <v>1</v>
       </c>
       <c r="G45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>12304</v>
+      </c>
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>58001</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>96</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>12304</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" t="s">
         <v>97</v>
       </c>
-      <c r="F46" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>32102</v>
-      </c>
-      <c r="B47" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
         <v>98</v>
       </c>
-      <c r="D47" t="s">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>12304</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
         <v>99</v>
       </c>
-      <c r="E47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>32102</v>
-      </c>
-      <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" t="s">
         <v>100</v>
       </c>
-      <c r="D48" t="s">
-        <v>37</v>
-      </c>
-      <c r="F48" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
+      <c r="D49" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>32102</v>
-      </c>
-      <c r="B49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="E49" t="s">
         <v>102</v>
       </c>
-      <c r="D49" t="s">
-        <v>79</v>
-      </c>
       <c r="F49" t="b">
         <v>1</v>
       </c>
-      <c r="G49" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>10000</v>
+      <c r="A50" s="8">
+        <v>10603</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
-      </c>
-      <c r="E50" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>10000</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="3" t="s">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>10603</v>
+      </c>
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>10603</v>
+      </c>
+      <c r="B52" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>15601</v>
+      </c>
+      <c r="B53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>15201</v>
-      </c>
-      <c r="B52" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="D53" t="s">
         <v>127</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>15601</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" t="s">
         <v>128</v>
       </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>15201</v>
-      </c>
-      <c r="B53" t="s">
-        <v>19</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="D54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
         <v>129</v>
       </c>
-      <c r="D53" t="s">
-        <v>45</v>
-      </c>
-      <c r="F53" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" t="s">
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>15601</v>
+      </c>
+      <c r="B55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>15201</v>
-      </c>
-      <c r="B54" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="D55" t="s">
         <v>131</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>10308</v>
+      </c>
+      <c r="B56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
         <v>132</v>
       </c>
-      <c r="F54" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>61001</v>
-      </c>
-      <c r="B55" t="s">
-        <v>33</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="D56" t="s">
         <v>133</v>
       </c>
-      <c r="D55" t="s">
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>10308</v>
+      </c>
+      <c r="B57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" t="s">
         <v>134</v>
       </c>
-      <c r="F55" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>61001</v>
-      </c>
-      <c r="B56" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="D57" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
         <v>135</v>
       </c>
-      <c r="D56" t="s">
-        <v>45</v>
-      </c>
-      <c r="F56" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>10308</v>
+      </c>
+      <c r="B58" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>61001</v>
-      </c>
-      <c r="B57" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="D58" t="s">
         <v>137</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>15602</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
         <v>138</v>
       </c>
-      <c r="F57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>13008</v>
-      </c>
-      <c r="B58" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="D59" t="s">
         <v>139</v>
       </c>
-      <c r="D58" t="s">
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>15602</v>
+      </c>
+      <c r="B60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" t="s">
         <v>140</v>
       </c>
-      <c r="F58" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>13008</v>
-      </c>
-      <c r="B59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="D60" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
         <v>141</v>
       </c>
-      <c r="D59" t="s">
-        <v>45</v>
-      </c>
-      <c r="F59" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>15602</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>13008</v>
-      </c>
-      <c r="B60" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="D61" t="s">
         <v>143</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>10309</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
         <v>144</v>
       </c>
-      <c r="F60" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>61002</v>
-      </c>
-      <c r="B61" t="s">
-        <v>33</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="D62" t="s">
         <v>145</v>
       </c>
-      <c r="D61" t="s">
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <v>10309</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" t="s">
         <v>146</v>
       </c>
-      <c r="F61" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>61002</v>
-      </c>
-      <c r="B62" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
         <v>147</v>
       </c>
-      <c r="D62" t="s">
-        <v>45</v>
-      </c>
-      <c r="F62" t="b">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>10309</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>61002</v>
-      </c>
-      <c r="B63" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="D64" t="s">
         <v>149</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
+        <v>10310</v>
+      </c>
+      <c r="B65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" t="s">
         <v>150</v>
       </c>
-      <c r="F63" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>13009</v>
-      </c>
-      <c r="B64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="D65" t="s">
         <v>151</v>
       </c>
-      <c r="D64" t="s">
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>10310</v>
+      </c>
+      <c r="B66" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s">
         <v>152</v>
       </c>
-      <c r="F64" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>13009</v>
-      </c>
-      <c r="B65" t="s">
-        <v>19</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="D66" t="s">
+        <v>42</v>
+      </c>
+      <c r="F66" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
         <v>153</v>
       </c>
-      <c r="D65" t="s">
-        <v>45</v>
-      </c>
-      <c r="F65" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s">
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="8">
+        <v>10310</v>
+      </c>
+      <c r="B67" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>13009</v>
-      </c>
-      <c r="B66" t="s">
-        <v>19</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="D67" t="s">
         <v>155</v>
       </c>
-      <c r="D66" t="s">
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>15501</v>
+      </c>
+      <c r="B68" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" t="s">
         <v>156</v>
       </c>
-      <c r="F66" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>13010</v>
-      </c>
-      <c r="B67" t="s">
-        <v>33</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="D68" t="s">
         <v>157</v>
       </c>
-      <c r="D67" t="s">
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <v>15501</v>
+      </c>
+      <c r="B69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" t="s">
         <v>158</v>
       </c>
-      <c r="F67" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>13010</v>
-      </c>
-      <c r="B68" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="D69" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
         <v>159</v>
       </c>
-      <c r="D68" t="s">
-        <v>45</v>
-      </c>
-      <c r="F68" t="b">
-        <v>1</v>
-      </c>
-      <c r="G68" t="s">
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <v>15501</v>
+      </c>
+      <c r="B70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>13010</v>
-      </c>
-      <c r="B69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="D70" t="s">
         <v>161</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>10403</v>
+      </c>
+      <c r="B71" t="s">
+        <v>30</v>
+      </c>
+      <c r="C71" t="s">
         <v>162</v>
       </c>
-      <c r="F69" t="b">
-        <v>1</v>
-      </c>
-      <c r="G69" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>60001</v>
-      </c>
-      <c r="B70" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="D71" t="s">
         <v>163</v>
       </c>
-      <c r="D70" t="s">
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>10403</v>
+      </c>
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" t="s">
         <v>164</v>
       </c>
-      <c r="F70" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>60001</v>
-      </c>
-      <c r="B71" t="s">
-        <v>19</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="D72" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
         <v>165</v>
       </c>
-      <c r="D71" t="s">
-        <v>45</v>
-      </c>
-      <c r="F71" t="b">
-        <v>1</v>
-      </c>
-      <c r="G71" t="s">
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>10403</v>
+      </c>
+      <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>60001</v>
-      </c>
-      <c r="B72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="D73" t="s">
         <v>167</v>
       </c>
-      <c r="D72" t="s">
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>15603</v>
+      </c>
+      <c r="B74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" t="s">
         <v>168</v>
       </c>
-      <c r="F72" t="b">
-        <v>1</v>
-      </c>
-      <c r="G72" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>141001</v>
-      </c>
-      <c r="B73" t="s">
-        <v>33</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="D74" t="s">
         <v>169</v>
       </c>
-      <c r="D73" t="s">
+      <c r="F74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>15603</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
         <v>170</v>
       </c>
-      <c r="F73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>141001</v>
-      </c>
-      <c r="B74" t="s">
-        <v>19</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="D75" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
         <v>171</v>
       </c>
-      <c r="D74" t="s">
-        <v>45</v>
-      </c>
-      <c r="F74" t="b">
-        <v>1</v>
-      </c>
-      <c r="G74" t="s">
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>15603</v>
+      </c>
+      <c r="B76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>141001</v>
-      </c>
-      <c r="B75" t="s">
-        <v>19</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="D76" t="s">
         <v>173</v>
       </c>
-      <c r="D75" t="s">
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>15301</v>
+      </c>
+      <c r="B77" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" t="s">
         <v>174</v>
       </c>
-      <c r="F75" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>61003</v>
-      </c>
-      <c r="B76" t="s">
-        <v>33</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="D77" t="s">
         <v>175</v>
       </c>
-      <c r="D76" t="s">
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>15301</v>
+      </c>
+      <c r="B78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" t="s">
         <v>176</v>
       </c>
-      <c r="F76" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>61003</v>
-      </c>
-      <c r="B77" t="s">
-        <v>19</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="D78" t="s">
+        <v>42</v>
+      </c>
+      <c r="F78" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" t="s">
         <v>177</v>
       </c>
-      <c r="D77" t="s">
-        <v>45</v>
-      </c>
-      <c r="F77" t="b">
-        <v>1</v>
-      </c>
-      <c r="G77" t="s">
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <v>15301</v>
+      </c>
+      <c r="B79" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>61003</v>
-      </c>
-      <c r="B78" t="s">
-        <v>19</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="D79" t="s">
         <v>179</v>
       </c>
-      <c r="D78" t="s">
+      <c r="F79" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>15604</v>
+      </c>
+      <c r="B80" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" t="s">
         <v>180</v>
       </c>
-      <c r="F78" t="b">
-        <v>1</v>
-      </c>
-      <c r="G78" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>59101</v>
-      </c>
-      <c r="B79" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="D80" t="s">
         <v>181</v>
       </c>
-      <c r="D79" t="s">
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="8">
+        <v>15604</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" t="s">
         <v>182</v>
       </c>
-      <c r="F79" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>59101</v>
-      </c>
-      <c r="B80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="D81" t="s">
+        <v>42</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
         <v>183</v>
       </c>
-      <c r="D80" t="s">
-        <v>45</v>
-      </c>
-      <c r="F80" t="b">
-        <v>1</v>
-      </c>
-      <c r="G80" t="s">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>15604</v>
+      </c>
+      <c r="B82" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>59101</v>
-      </c>
-      <c r="B81" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="D82" t="s">
         <v>185</v>
       </c>
-      <c r="D81" t="s">
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>15605</v>
+      </c>
+      <c r="B83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" t="s">
         <v>186</v>
       </c>
-      <c r="F81" t="b">
-        <v>1</v>
-      </c>
-      <c r="G81" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>61004</v>
-      </c>
-      <c r="B82" t="s">
-        <v>33</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="D83" t="s">
         <v>187</v>
       </c>
-      <c r="D82" t="s">
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>15605</v>
+      </c>
+      <c r="B84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" t="s">
         <v>188</v>
       </c>
-      <c r="F82" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>61004</v>
-      </c>
-      <c r="B83" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="D84" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" t="s">
         <v>189</v>
       </c>
-      <c r="D83" t="s">
-        <v>45</v>
-      </c>
-      <c r="F83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G83" t="s">
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>15605</v>
+      </c>
+      <c r="B85" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>61004</v>
-      </c>
-      <c r="B84" t="s">
-        <v>19</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="D85" t="s">
         <v>191</v>
       </c>
-      <c r="D84" t="s">
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>10604</v>
+      </c>
+      <c r="B86" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" t="s">
         <v>192</v>
       </c>
-      <c r="F84" t="b">
-        <v>1</v>
-      </c>
-      <c r="G84" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>61005</v>
-      </c>
-      <c r="B85" t="s">
-        <v>33</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="D86" t="s">
         <v>193</v>
       </c>
-      <c r="D85" t="s">
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <v>10604</v>
+      </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" t="s">
         <v>194</v>
       </c>
-      <c r="F85" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>61005</v>
-      </c>
-      <c r="B86" t="s">
-        <v>19</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="D87" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
         <v>195</v>
       </c>
-      <c r="D86" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" t="b">
-        <v>1</v>
-      </c>
-      <c r="G86" t="s">
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>10604</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>61005</v>
-      </c>
-      <c r="B87" t="s">
-        <v>19</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="D88" t="s">
+        <v>191</v>
+      </c>
+      <c r="F88" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>10311</v>
+      </c>
+      <c r="B89" t="s">
+        <v>30</v>
+      </c>
+      <c r="C89" t="s">
         <v>197</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D89" t="s">
         <v>198</v>
       </c>
-      <c r="F87" t="b">
-        <v>1</v>
-      </c>
-      <c r="G87" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>15202</v>
-      </c>
-      <c r="B88" t="s">
-        <v>33</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="F89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>10311</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
         <v>199</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D90" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" t="s">
         <v>200</v>
       </c>
-      <c r="F88" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>15202</v>
-      </c>
-      <c r="B89" t="s">
-        <v>19</v>
-      </c>
-      <c r="C89" t="s">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <v>10311</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" t="s">
         <v>201</v>
       </c>
-      <c r="D89" t="s">
-        <v>45</v>
-      </c>
-      <c r="F89" t="b">
-        <v>1</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="D91" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>15202</v>
-      </c>
-      <c r="B90" t="s">
-        <v>19</v>
-      </c>
-      <c r="C90" t="s">
-        <v>203</v>
-      </c>
-      <c r="D90" t="s">
-        <v>198</v>
-      </c>
-      <c r="F90" t="b">
-        <v>1</v>
-      </c>
-      <c r="G90" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>13011</v>
-      </c>
-      <c r="B91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C91" t="s">
-        <v>204</v>
-      </c>
-      <c r="D91" t="s">
-        <v>205</v>
-      </c>
       <c r="F91" t="b">
         <v>1</v>
+      </c>
+      <c r="G91" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>13011</v>
+        <v>10000</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="C92" t="s">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
       </c>
-      <c r="G92" t="s">
-        <v>207</v>
+      <c r="H92" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>13011</v>
+        <v>10000</v>
       </c>
       <c r="B93" t="s">
         <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>10000</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>107</v>
+      <c r="B94" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" t="s">
+        <v>110</v>
+      </c>
+      <c r="D94" t="s">
+        <v>111</v>
+      </c>
+      <c r="F94" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -3256,19 +3266,19 @@
         <v>10000</v>
       </c>
       <c r="B95" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" t="s">
+        <v>113</v>
+      </c>
+      <c r="D95" t="s">
         <v>108</v>
       </c>
-      <c r="C95" t="s">
-        <v>109</v>
-      </c>
-      <c r="D95" t="s">
-        <v>110</v>
-      </c>
       <c r="F95" t="b">
         <v>1</v>
       </c>
-      <c r="H95" t="s">
-        <v>111</v>
+      <c r="G95" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -3276,42 +3286,42 @@
         <v>10000</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="C96" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
       </c>
-      <c r="G96" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H96" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>10000</v>
       </c>
       <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" t="s">
+        <v>118</v>
+      </c>
+      <c r="D97" t="s">
         <v>108</v>
       </c>
-      <c r="C97" t="s">
-        <v>115</v>
-      </c>
-      <c r="D97" t="s">
-        <v>116</v>
-      </c>
       <c r="F97" t="b">
         <v>1</v>
       </c>
-      <c r="H97" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G97" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>10000</v>
       </c>
@@ -3319,39 +3329,27 @@
         <v>19</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>203</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
+        <v>204</v>
       </c>
       <c r="F98" t="b">
-        <v>1</v>
-      </c>
-      <c r="G98" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>10000</v>
       </c>
-      <c r="B99" t="s">
-        <v>108</v>
-      </c>
-      <c r="C99" t="s">
-        <v>120</v>
-      </c>
-      <c r="D99" t="s">
-        <v>121</v>
-      </c>
-      <c r="F99" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B99" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>10000</v>
       </c>
@@ -3359,63 +3357,21 @@
         <v>19</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>297</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>298</v>
       </c>
       <c r="F100" t="b">
-        <v>1</v>
-      </c>
-      <c r="G100" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>10000</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>10000</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>10000</v>
-      </c>
-      <c r="B103" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D103" t="s">
-        <v>211</v>
-      </c>
-      <c r="F103" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C95:C100">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  <conditionalFormatting sqref="C7">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+  <conditionalFormatting sqref="C92:C97">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3434,10 +3390,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -3446,7 +3402,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3454,13 +3410,13 @@
         <v>10000</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3468,13 +3424,13 @@
         <v>10000</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3482,16 +3438,16 @@
         <v>10000</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3499,16 +3455,16 @@
         <v>10000</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D5" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3516,16 +3472,16 @@
         <v>10000</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C6" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3533,16 +3489,16 @@
         <v>10000</v>
       </c>
       <c r="B7" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D7" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E7" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3550,16 +3506,16 @@
         <v>10000</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C8" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D8" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3567,16 +3523,16 @@
         <v>10000</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -3584,16 +3540,16 @@
         <v>10000</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E10" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3601,16 +3557,16 @@
         <v>10000</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C11" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E11" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3618,16 +3574,16 @@
         <v>10000</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D12" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -3635,16 +3591,16 @@
         <v>10000</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E13" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3652,13 +3608,13 @@
         <v>10000</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3666,13 +3622,13 @@
         <v>10000</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3680,16 +3636,16 @@
         <v>10000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3697,16 +3653,16 @@
         <v>10000</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3714,16 +3670,16 @@
         <v>10000</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3731,16 +3687,16 @@
         <v>10000</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3748,16 +3704,16 @@
         <v>10000</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3765,16 +3721,16 @@
         <v>10000</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3782,16 +3738,16 @@
         <v>10000</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3799,16 +3755,16 @@
         <v>10000</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3816,16 +3772,16 @@
         <v>10000</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3833,16 +3789,16 @@
         <v>10000</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3850,16 +3806,16 @@
         <v>10000</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3867,16 +3823,16 @@
         <v>10000</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3884,13 +3840,13 @@
         <v>10000</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C28" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D28" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3898,13 +3854,13 @@
         <v>10000</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3912,13 +3868,13 @@
         <v>10000</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D30" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3926,13 +3882,13 @@
         <v>10000</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D31" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3940,13 +3896,13 @@
         <v>10000</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D32" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3954,13 +3910,13 @@
         <v>10000</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C33" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D33" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3968,13 +3924,13 @@
         <v>10000</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" t="s">
         <v>220</v>
       </c>
-      <c r="C34" t="s">
-        <v>227</v>
-      </c>
       <c r="D34" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3982,13 +3938,13 @@
         <v>10000</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C35" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D35" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3996,13 +3952,13 @@
         <v>10000</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C36" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D36" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -4010,13 +3966,13 @@
         <v>10000</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D37" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -4024,13 +3980,13 @@
         <v>10000</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C38" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D38" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -4038,13 +3994,13 @@
         <v>10000</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D39" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -4052,13 +4008,13 @@
         <v>10000</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C40" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -4066,13 +4022,13 @@
         <v>10000</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C41" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -4080,13 +4036,13 @@
         <v>10000</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D42" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -4094,13 +4050,13 @@
         <v>10000</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C43" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -4122,20 +4078,20 @@
       <c r="B49" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C31:C43">
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C4:C6">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C10">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C27">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31:C43">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4148,24 +4104,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -4185,15 +4141,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
     <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
@@ -4434,6 +4381,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57DADB5E-A934-4F74-9E46-6B0166AE6702}">
   <ds:schemaRefs>
@@ -4448,14 +4404,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44DF40B5-A208-41D6-91DF-C6FBF19622EA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2CAB3E8-13F0-4618-9726-90B6A33E9E1E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4472,4 +4420,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44DF40B5-A208-41D6-91DF-C6FBF19622EA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/resources/tool_kii_community_iphra_v2.xlsx
+++ b/resources/tool_kii_community_iphra_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8DFBE0-F5CC-498B-9BD8-491F34B8C948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79607038-C25D-402E-9104-C220613379ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18210" yWindow="840" windowWidth="14535" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="312">
   <si>
     <t>type</t>
   </si>
@@ -977,6 +977,45 @@
   </si>
   <si>
     <t>Do you as the interviewer have any further comments or observations?</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
+  </si>
+  <si>
+    <t>Homme</t>
+  </si>
+  <si>
+    <t>Femme</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1118,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3368,10 +3417,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92:C97">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3379,7 +3428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3418,6 +3467,9 @@
       <c r="D2" s="6" t="s">
         <v>244</v>
       </c>
+      <c r="E2" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="3" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -3432,6 +3484,9 @@
       <c r="D3" s="6" t="s">
         <v>242</v>
       </c>
+      <c r="E3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -3616,6 +3671,9 @@
       <c r="D14" s="6" t="s">
         <v>248</v>
       </c>
+      <c r="E14" s="6" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="15" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3630,22 +3688,25 @@
       <c r="D15" s="6" t="s">
         <v>246</v>
       </c>
+      <c r="E15" s="6" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>10000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>280</v>
+        <v>299</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3653,16 +3714,16 @@
         <v>10000</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>283</v>
+        <v>299</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3670,16 +3731,16 @@
         <v>10000</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>284</v>
+        <v>299</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3687,16 +3748,16 @@
         <v>10000</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>286</v>
+        <v>299</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3704,16 +3765,16 @@
         <v>10000</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>287</v>
+        <v>299</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3721,10 +3782,10 @@
         <v>10000</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>281</v>
@@ -3738,10 +3799,10 @@
         <v>10000</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>281</v>
@@ -3755,10 +3816,10 @@
         <v>10000</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>281</v>
@@ -3772,10 +3833,10 @@
         <v>10000</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>281</v>
@@ -3789,10 +3850,10 @@
         <v>10000</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>281</v>
@@ -3806,10 +3867,10 @@
         <v>10000</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>281</v>
@@ -3823,10 +3884,10 @@
         <v>10000</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>281</v>
@@ -3835,74 +3896,89 @@
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>10000</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C28" t="s">
-        <v>207</v>
-      </c>
-      <c r="D28" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>10000</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C29" t="s">
-        <v>209</v>
-      </c>
-      <c r="D29" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>10000</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C30" t="s">
-        <v>211</v>
-      </c>
-      <c r="D30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>10000</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D31" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>10000</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" t="s">
-        <v>216</v>
-      </c>
-      <c r="D32" t="s">
-        <v>217</v>
+      <c r="B32" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3910,13 +3986,13 @@
         <v>10000</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D33" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3924,13 +4000,13 @@
         <v>10000</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D34" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3938,13 +4014,13 @@
         <v>10000</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D35" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3955,10 +4031,10 @@
         <v>213</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D36" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3969,10 +4045,10 @@
         <v>213</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D37" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3983,10 +4059,10 @@
         <v>213</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D38" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3997,10 +4073,10 @@
         <v>213</v>
       </c>
       <c r="C39" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D39" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -4011,10 +4087,10 @@
         <v>213</v>
       </c>
       <c r="C40" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D40" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -4025,10 +4101,10 @@
         <v>213</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -4039,10 +4115,10 @@
         <v>213</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -4053,45 +4129,118 @@
         <v>213</v>
       </c>
       <c r="C43" t="s">
+        <v>228</v>
+      </c>
+      <c r="D43" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C44" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D45" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C46" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C47" t="s">
+        <v>236</v>
+      </c>
+      <c r="D47" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" t="s">
         <v>238</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D48" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="3"/>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="3"/>
     </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="3"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="3"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C10">
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
+  <conditionalFormatting sqref="C21:C32">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C27">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="C36:C48">
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C31:C43">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  <conditionalFormatting sqref="C16:C20">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4130,14 +4279,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4382,23 +4529,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57DADB5E-A934-4F74-9E46-6B0166AE6702}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44DF40B5-A208-41D6-91DF-C6FBF19622EA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c"/>
-    <ds:schemaRef ds:uri="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4423,9 +4567,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44DF40B5-A208-41D6-91DF-C6FBF19622EA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57DADB5E-A934-4F74-9E46-6B0166AE6702}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c"/>
+    <ds:schemaRef ds:uri="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>